--- a/tools/cfgtool/xls/DropItem.xlsx
+++ b/tools/cfgtool/xls/DropItem.xlsx
@@ -8,23 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkCode\tools\bf_xlsx_tool\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261E5298-56C2-4291-A1B3-650C01A4D7EF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14175"/>
   </bookViews>
   <sheets>
     <sheet name="掉落表" sheetId="1" r:id="rId1"/>
     <sheet name="生成表" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">掉落表!$A$5:$I$9</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">掉落表!$A$5:$I$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>DropItemId</t>
   </si>
@@ -116,39 +115,42 @@
   <si>
     <t>client</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>@config:xlsx_config|掉落表:DropItemConfig|map:DropItemId</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -201,22 +203,22 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -365,7 +367,7 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -378,7 +380,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -955,14 +957,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="52.375" customWidth="1"/>
+    <col customWidth="true" max="1" min="1" width="52.375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
